--- a/SINGLE HADITH CONTENT/missing_input/[V1] MUWATTA-MALIK-BANGLA_missing.xlsx
+++ b/SINGLE HADITH CONTENT/missing_input/[V1] MUWATTA-MALIK-BANGLA_missing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1976,6 +1976,482 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي يَحْيَى عَنْ مَالِك عَنْ هِشَامِ بْنِ عُرْوَةَ عَنْ أَسْمَاءَ بِنْتِ أَبِي بَكْرٍ أَنَّهَا قَالَتْ لِأَهْلِهَا أَجْمِرُوا ثِيَابِي إِذَا مِتُّ ثُمَّ حَنِّطُونِي وَلَا تَذُرُّوا عَلَى كَفَنِي حِنَاطًا وَلَا تَتْبَعُونِي بِنَارٍ.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>আস্মা বিন্ত আবূ বক্‌র (রা) নিজের পরিবারের লোকদেরকে বলেছেন, আমার মৃত্যু হলে আমার কাপড়কে (কাফন) খোশবুমুক্ত করো, তারপর আমার দেহে হানূত (কাপূর, মিশ্কে আম্বর ইত্যাতি দ্বারা তৈরি এক প্রকারের খোশবু) লাগাবে। কিন্তু হানূত আমার কাফনে ছিটাবে না, আর আগুন সাথে নিয়ে আমার পেছনে চলবে না। (ইবনু আসাকীর হাদীসটি তাখরীজ করেন [তারীখে দামেশক] তারীখে দামেশক ৭৩/২১, ইমাম মাইলায়ী হাদীসটিকে সহীহ বলেছেন, নসবুর রয়াহ ২/২৬৪)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي عَنْ مَالِك عَنْ سَعِيدِ بْنِ أَبِي سَعِيدٍ الْمَقْبُرِيِّ عَنْ أَبِي هُرَيْرَةَ أَنَّهُ نَهَى أَنْ يُتْبَعَ بَعْدَ مَوْتِهِ بِنَارٍ قَالَ يَحْيَى سَمِعْت قَوْله تَعَالَى يَكْرَهُ ذَلِكَ.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>আবূ হুরায়রা (রা) তার মৃত্যুর পর পেছনে আগুন নিয়ে চলতে নিষেধ করেছেন। (সহীহ, আহমাদ ২/৪২৭, আলবানী হাদীসটিকে সহীহ বলেছেন, [আহকামুল জানায়েজ পৃঃ ৭০]) ইয়াহ্ইয়া (র) বললেন, আমি শুনেছি যে, মালিক (র) একে মাকরূহ জানতেন।</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي يَحْيَى عَنْ مَالِك عَنْ مُحَمَّدِ بْنِ أَبِي بَكْرِ بْنِ مُحَمَّدِ بْنِ عَمْرِو بْنِ حَزْمٍ عَنْ عَبْدِ الرَّحْمَنِ بْنِ حَنْظَلَةَ الزُّرَقِيِّ أَنَّهُ أَخْبَرَهُ عَنْ مَوْلًى لِقُرَيْشٍ كَانَ قَدِيمًا يُقَالُ لَهُ ابْنُ مِرْسَى أَنَّهُ قَالَ كُنْتُ جَالِسًا عِنْدَ عُمَرَ بْنِ الْخَطَّابِ فَلَمَّا صَلَّى الظُّهْرَ قَالَ يَا يَرْفَا هَلُمَّ ذَلِكَ الْكِتَابَ لِكِتَابٍ كَتَبَهُ فِي شَأْنِ الْعَمَّةِ فَنَسْأَلَ عَنْهَا وَنَسْتَخْبِرَ عَنْهَا فَأَتَاهُ بِهِ يَرْفَا فَدَعَا بِتَوْرٍ أَوْ قَدَحٍ فِيهِ مَاءٌ فَمَحَا ذَلِكَ الْكِتَابَ فِيهِ ثُمَّ قَالَ لَوْ رَضِيَكِ اللهُ وَارِثَةً أَقَرَّكِ لَوْ رَضِيَكِ اللهُ أَقَرَّكِ.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>আমি উমার ইবনু খাত্তাব (রা)-এর নিকট বসা ছিলাম, তিনি যুহরের নামায পড়ে য়ারফা নামক সাহাবীকে বললেন, আমার নিকট ঐ কিতাবটি নিয়ে আস, যা ফুফুর মীরাস সম্বন্ধে লেখা হয়েছে। আমি এব্যাপারে লোকের নিকট জিজ্ঞেস করব। অতঃপর উমার (রা) একটি পেয়ালা আনলেন যাতে পানি ছিল। ঐ পানি দ্বারা ঐ কিতাব ধুয়ে ফেললেন এবং বললেন, যদি ফুফুকে অংশ দেয়া আল্লাহর ইচ্ছা থাকত তা হলে স্বীয় কিতাবে উহা উল্লেখ করতেন। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي عَنْ مَالِك عَنْ مُحَمَّدِ بْنِ أَبِي بَكْرِ بْنِ حَزْمٍ أَنَّهُ سَمِعَ أَبَاهُ كَثِيرًا يَقُولُ كَانَ عُمَرُ بْنُ الْخَطَّابِ يَقُولُ عَجَبًا لِلْعَمَّةِ تُورَثُ وَلَا تَرِثُ.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>তিনি তার পিতাকে অনেক বার বলতে শুনেছেন যে, উমার ইবনু খাত্তাব (রা) বলতেন, ফুফুর ব্যাপার আশ্চর্যজনক, তিনি মীরাস পান না কিন্তু তার মীরাস অন্যরা পায়। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي يَحْيَى عَنْ مَالِك عَنْ رَبِيعَةَ بْنِ أَبِي عَبْدِ الرَّحْمَنِ عَنْ غَيْرِ وَاحِدٍ مِنْ عُلَمَائِهِمْ أَنَّهُ لَمْ يَتَوَارَثْ مَنْ قُتِلَ يَوْمَ الْجَمَلِ وَيَوْمَ صِفِّينَ وَيَوْمَ الْحَرَّةِ ثُمَّ كَانَ يَوْمَ قُدَيْدٍ فَلَمْ يُوَرَّثْ أَحَدٌ مِنْ صَاحِبِهِ شَيْئًا إِلَّا مَنْ عُلِمَ أَنَّهُ قُتِلَ قَبْلَ صَاحِبِهِ ১৯قَالَ مَالِك وَذَلِكَ الْأَمْرُ الَّذِي لَا اخْتِلَافَ فِيهِ وَلَا شَكَّ عِنْدَ أَحَدٍ مِنْ أَهْلِ الْعِلْمِ بِبَلَدِنَا وَكَذَلِكَ الْعَمَلُ فِي كُلِّ مُتَوَارِثَيْنِ هَلَكَا بِغَرَقٍ أَوْ قَتْلٍ أَوْ غَيْرِ ذَلِكَ مِنْ الْمَوْتِ إِذَا لَمْ يُعْلَمْ أَيُّهُمَا مَاتَ قَبْلَ صَاحِبِهِ لَمْ يَرِثْ أَحَدٌ مِنْهُمَا مِنْ صَاحِبِهِ شَيْئًا وَكَانَ مِيرَاثُهُمَا لِمَنْ بَقِيَ مِنْ وَرَثَتِهِمَا يَرِثُ كُلَّ وَاحِدٍ مِنْهُمَا وَرَثَتُهُ مِنْ الْأَحْيَاء ১৯و قَالَ مَالِك لَا يَنْبَغِي أَنْ يَرِثَ أَحَدٌ أَحَدًا بِالشَّكِّ وَلَا يَرِثُ أَحَدٌ أَحَدًا إِلَّا بِالْيَقِينِ مِنْ الْعِلْمِ وَالشُّهَدَاءِ وَذَلِكَ أَنَّ الرَّجُلَ يَهْلَكُ هُوَ وَمَوْلَاهُ الَّذِي أَعْتَقَهُ أَبُوهُ فَيَقُولُ بَنُو الرَّجُلِ الْعَرَبِيِّ قَدْ وَرِثَهُ أَبُونَا فَلَيْسَ ذَلِكَ لَهُمْ أَنْ يَرِثُوهُ بِغَيْرِ عِلْمٍ وَلَا شَهَادَةٍ إِنَّهُ مَاتَ قَبْلَهُ وَإِنَّمَا يَرِثُهُ أَوْلَى النَّاسِ بِهِ مِنْ الْأَحْيَاءِ. قَالَ مَالِك وَمِنْ ذَلِكَ أَيْضًا الْأَخَوَانِ لِلْأَبِ وَالْأُمِّ يَمُوتَانِ وَلِأَحَدِهِمَا وَلَدٌ وَالْآخَرُ لَا وَلَدَ لَهُ وَلَهُمَا أَخٌ لِأَبِيهِمَا فَلَا يُعْلَمُ أَيُّهُمَا مَاتَ قَبْلَ صَاحِبِهِ فَمِيرَاثُ الَّذِي لَا وَلَدَ لَهُ لِأَخِيهِ لِأَبِيهِ وَلَيْسَ لِبَنِي أَخِيهِ لِأَبِيهِ وَأُمِّهِ شَيْءٌ. قَالَ مَالِك وَمِنْ ذَلِكَ أَيْضًا أَنْ تَهْلَكَ الْعَمَّةُ وَابْنُ أَخِيهَا أَوْ ابْنَةُ الْأَخِ وَعَمُّهَا فَلَا يُعْلَمُ أَيُّهُمَا مَاتَ قَبْلُ فَإِنْ لَمْ يُعْلَمْ أَيُّهُمَا مَاتَ قَبْلُ لَمْ يَرِثْ الْعَمُّ مِنْ ابْنَةِ أَخِيهِ شَيْئًا وَلَا يَرِثُ ابْنُ الْأَخِ مِنْ عَمَّتِهِ شَيْئًا ِِِِ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>একাধিক আলেম সূত্রে বর্ণনা করেন যে, জামাল যুদ্ধে, সিফফীন যুদ্ধে এবং হাররা দিবসে যারা নিহত হয়েছেন তারা মীরাস পাননি। এরপর ফুদাইদ দিবসে যারা নিহত হয়েছে তারাও একে অপরের মীরাস পাননি। কিন্তু মীরাস পাবে সেই ক্ষেত্রে যেই ক্ষেত্রে নিশ্চিত জানা গিয়েছে যে, তিনি তার সাথির পূর্বে নিহত হয়েছেন। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) ইয়াহইয়া (র) বলেন : আমি মালিক (র)-কে বলতে শুনেছি, আমাদের ‘উলামায়ে কিরামের মধ্যে এ ব্যাপারে কোন বিরোধ নাই। মালিক (র) বলেন : যদি কয়েকজন পানিতে ডুবে অথবা মাটিতে ধ্বসে মৃত্যুবরণ করে অথবা নিহত হয়, আর কে আগে কে পরে মৃত্যুবরণ করেছে তা অজ্ঞাত থাকে তবে তারা এক অন্যের ওয়ারিস হবে না, বরং প্রত্যেকের মাল তাদের ওয়ারিসগণ পাবে, যারা জীবিত রয়েছে। মালিক (র) বলেন : কেউ সন্দেহস্থলে কারো ওয়ারিস হবে না, ওয়ারিস হওয়ার জন্য নিঃসন্দেহ হওয়া প্রয়োজন। যেমন কেউ মৃত্যুবরণ করলে, আর সে তার যে দাসকে মুক্ত করেছিল সেও মৃত্যুবরণ করল, এখন যদি এই সন্তান বলে যে, আমার পিতা এই দাসের ওয়ারিস হবে তবে তা ততক্ষণ পর্যন্ত সাব্যস্ত হবে না যতক্ষণ না সে সাক্ষী দ্বারা প্রমাণ করবে যে, ঐ দাস তার পিতার পূর্বে মারা গিয়েছে। যদি প্রমাণ করতে না পারে তবে ঐ দাসের জীবিত ওয়ারিসগণ তার মাল পাবে। মালিক (র) বলেন, অনুরূপভাবে যদি দুই সহোদর ভাই মারা যায় যাদের একজনের সন্তান রয়েছে অন্যজন নিঃসন্তান, আর তাদের উভয়ের একজন সৎ ভাইও রয়েছে। কিন্তু এটা জানা যায়নি যে, প্রথমে কোন ভাই মরেছে। এখন নিঃসন্তান ভাই-এর মাল তার সৎ ভাই পাবে, তার ভাতিজারা পাবে না। এইরূপে ফুফু ভাতিজা একত্রে মারা গেলে বা চাচা ভাতিজা একত্রে মারা গেলে আর কে আগে মারা গিয়েছে তা জানা নাই, তবে চাচা স্বীয় ভাতিজার এবং ভাতিজা স্বীয় ফুফুর ওয়ারিস হবে না।</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>و عَنْ مَالِك عَنْ أَبِي الزِّنَادِ أَنَّ عُمَرَ بْنَ عَبْدِ الْعَزِيزِ كَتَبَ إِلَى عَبْدِ الْحَمِيدِ بْنِ عَبْدِ الرَّحْمَنِ بْنِ زَيْدِ بْنِ الْخَطَّابِ وَهُوَ عَامِلٌ عَلَى الْكُوفَةِ أَنْ اقْضِ بِالْيَمِينِ مَعَ الشَّاهِدِ.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>উমার ইব্নু আবদিল আযীয (র) কুফার শাসনকর্তা আবদুল হামিদ ইব্নু আবদির রহমানকে লিখে পাঠালেন যে, (এক) সাক্ষীর সাথে কসম গ্রহণ করে ফয়সালা করে নিতে পার। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي مَالِك أَنَّهُ بَلَغَهُ أَنَّ أَبَا سَلَمَةَ بْنَ عَبْدِ الرَّحْمَنِ وَسُلَيْمَانَ بْنَ يَسَارٍ سُئِلَا هَلْ يُقْضَى بِالْيَمِينِ مَعَ الشَّاهِدِ فَقَالَا نَعَمْ قَالَ مَالِك مَضَتْ السُّنَّةُ فِي الْقَضَاءِ بِالْيَمِينِ مَعَ الشَّاهِدِ الْوَاحِدِ يَحْلِفُ صَاحِبُ الْحَقِّ مَعَ شَاهِدِهِ وَيَسْتَحِقُّ حَقَّهُ فَإِنْ نَكَلَ وَأَبَى أَنْ يَحْلِفَ أُحْلِفَ الْمَطْلُوبُ فَإِنْ حَلَفَ سَقَطَ عَنْهُ ذَلِكَ الْحَقُّ وَإِنْ أَبَى أَنْ يَحْلِفَ ثَبَتَ عَلَيْهِ الْحَقُّ لِصَاحِبِهِ قَالَ مَالِك وَإِنَّمَا يَكُونُ ذَلِكَ فِي الْأَمْوَالِ خَاصَّةً وَلَا يَقَعُ ذَلِكَ فِي شَيْءٍ مِنْ الْحُدُودِ وَلَا فِي نِكَاحٍ وَلَا فِي طَلَاقٍ وَلَا فِي عَتَاقَةٍ وَلَا فِي سَرِقَةٍ وَلَا فِي فِرْيَةٍ فَإِنْ قَالَ قَائِلٌ فَإِنَّ الْعَتَاقَةَ مِنْ الْأَمْوَالِ فَقَدْ أَخْطَأَ لَيْسَ ذَلِكَ عَلَى مَا قَالَ وَلَوْ كَانَ ذَلِكَ عَلَى مَا قَالَ لَحَلَفَ الْعَبْدُ مَعَ شَاهِدِهِ إِذَا جَاءَ بِشَاهِدٍ أَنَّ سَيِّدَهُ أَعْتَقَهُ وَأَنَّ الْعَبْدَ إِذَا جَاءَ بِشَاهِدٍ عَلَى مَالٍ مِنْ الْأَمْوَالِ ادَّعَاهُ حَلَفَ مَعَ شَاهِدِهِ وَاسْتَحَقَّ حَقَّهُ كَمَا يَحْلِفُ الْحُرُّ. قَالَ مَالِك فَالسُّنَّةُ عِنْدَنَا أَنَّ الْعَبْدَ إِذَا جَاءَ بِشَاهِدٍ عَلَى عَتَاقَتِهِ اسْتُحْلِفَ سَيِّدُهُ مَا أَعْتَقَهُ وَبَطَلَ ذَلِكَ عَنْهُ ২৬৭৭-قَالَ مَالِك وَكَذَلِكَ السُّنَّةُ عِنْدَنَا أَيْضًا فِي الطَّلَاقِ إِذَا جَاءَتْ الْمَرْأَةُ بِشَاهِدٍ أَنَّ زَوْجَهَا طَلَّقَهَا أُحْلِفَ زَوْجُهَا مَا طَلَّقَهَا فَإِذَا حَلَفَ لَمْ يَقَعْ عَلَيْهِ الطَّلَاقُ قَالَ مَالِك فَسُنَّةُ الطَّلَاقِ وَالْعَتَاقَةِ فِي الشَّاهِدِ الْوَاحِدِ وَاحِدَةٌ إِنَّمَا يَكُونُ الْيَمِينُ عَلَى زَوْجِ الْمَرْأَةِ وَعَلَى سَيِّدِ الْعَبْدِ وَإِنَّمَا الْعَتَاقَةُ حَدٌّ مِنْ الْحُدُودِ لَا تَجُوزُ فِيهَا شَهَادَةُ النِّسَاءِ لِأَنَّهُ إِذَا عَتَقَ الْعَبْدُ ثَبَتَتْ حُرْمَتُهُ وَوَقَعَتْ لَهُ الْحُدُودُ وَوَقَعَتْ عَلَيْهِ وَإِنْ زَنَى وَقَدْ أُحْصِنَ رُجِمَ وَإِنْ قَتَلَ الْعَبْدَ قُتِلَ بِهِ وَثَبَتَ لَهُ الْمِيرَاثُ بَيْنَهُ وَبَيْنَ مَنْ يُوَارِثُهُ فَإِنْ احْتَجَّ مُحْتَجٌّ فَقَالَ لَوْ أَنَّ رَجُلًا أَعْتَقَ عَبْدَهُ وَجَاءَ رَجُلٌ يَطْلُبُ سَيِّدَ الْعَبْدِ بِدَيْنٍ لَهُ عَلَيْهِ فَشَهِدَ لَهُ عَلَى حَقِّهِ ذَلِكَ رَجُلٌ وَامْرَأَتَانِ فَإِنَّ ذَلِكَ يُثْبِتُ الْحَقَّ عَلَى سَيِّدِ الْعَبْدِ حَتَّى تُرَدَّ بِهِ عَتَاقَتُهُ إِذَا لَمْ يَكُنْ لِسَيِّدِ الْعَبْدِ مَالٌ غَيْرُ الْعَبْدِ يُرِيدُ أَنْ يُجِيزَ بِذَلِكَ شَهَادَةَ النِّسَاءِ فِي الْعَتَاقَةِ فَإِنَّ ذَلِكَ لَيْسَ عَلَى مَا قَالَ وَإِنَّمَا مَثَلُ ذَلِكَ الرَّجُلُ يَعْتِقُ عَبْدَهُ ثُمَّ يَأْتِي طَالِبُ الْحَقِّ عَلَى سَيِّدِهِ بِشَاهِدٍ وَاحِدٍ فَيَحْلِفُ مَعَ شَاهِدِهِ ثُمَّ يَسْتَحِقُّ حَقَّهُ وَتُرَدُّ بِذَلِكَ عَتَاقَةُ الْعَبْدِ أَوْ يَأْتِي الرَّجُلُ قَدْ كَانَتْ بَيْنَهُ وَبَيْنَ سَيِّدِ الْعَبْدِ مُخَالَطَةٌ وَمُلَابَسَةٌ فَيَزْعُمُ أَنَّ لَهُ عَلَى سَيِّدِ الْعَبْدِ مَالًا فَيُقَالُ لِسَيِّدِ الْعَبْدِ احْلِفْ مَا عَلَيْكَ مَا ادَّعَى فَإِنْ نَكَلَ وَأَبَى أَنْ يَحْلِفَ حُلِّفَ صَاحِبُ الْحَقِّ وَثَبَتَ حَقُّهُ عَلَى سَيِّدِ الْعَبْدِ فَيَكُونُ ذَلِكَ يَرُدُّ عَتَاقَةَ الْعَبْدِ إِذَا ثَبَتَ الْمَالُ عَلَى سَيِّدِهِ. قَالَ وَكَذَلِكَ أَيْضًا الرَّجُلُ يَنْكِحُ الْأَمَةَ فَتَكُونُ امْرَأَتَهُ فَيَأْتِي سَيِّدُ الْأَمَةِ إِلَى الرَّجُلِ الَّذِي تَزَوَّجَهَا فَيَقُولُ ابْتَعْتَ مِنِّي جَارِيَتِي فُلَانَةَ أَنْتَ وَفُلَانٌ بِكَذَا وَكَذَا دِينَارًا فَيُنْكِرُ ذَلِكَ زَوْجُ الْأَمَةِ فَيَأْتِي سَيِّدُ الْأَمَةِ بِرَجُلٍ وَامْرَأَتَيْنِ فَيَشْهَدُونَ عَلَى مَا قَالَ فَيَثْبُتُ بَيْعُهُ وَيَحِقُّ حَقُّهُ وَتَحْرُمُ الْأَمَةُ عَلَى زَوْجِهَا وَيَكُونُ ذَلِكَ فِرَاقًا بَيْنَهُمَا وَشَهَادَةُ النِّسَاءِ لَا تَجُوزُ فِي الطَّلَاقِ قَالَ مَالِك وَمِنْ ذَلِكَ أَيْضًا الرَّجُلُ يَفْتَرِي عَلَى الرَّجُلِ الْحُرِّ فَيَقَعُ عَلَيْهِ الْحَدُّ فَيَأْتِي رَجُلٌ وَامْرَأَتَانِ فَيَشْهَدُونَ أَنَّ الَّذِي افْتُرِيَ عَلَيْهِ عَبْدٌ مَمْلُوكٌ فَيَضَعُ ذَلِكَ الْحَدَّ عَنْ الْمُفْتَرِي بَعْدَ أَنْ وَقَعَ عَلَيْهِ وَشَهَادَةُ النِّسَاءِ لَا تَجُوزُ فِي الْفِرْيَةِ قَالَ مَالِك وَمِمَّا يُشْبِهُ ذَلِكَ أَيْضًا مِمَّا يَفْتَرِقُ فِيهِ الْقَضَاءُ وَمَا مَضَى مِنْ السُّنَّةِ أَنَّ الْمَرْأَتَيْنِ يَشْهَدَانِ عَلَى اسْتِهْلَالِ الصَّبِيِّ فَيَجِبُ بِذَلِكَ مِيرَاثُهُ حَتَّى يَرِثَ وَيَكُونُ مَالُهُ لِمَنْ يَرِثُهُ إِنْ مَاتَ الصَّبِيُّ وَلَيْسَ مَعَ الْمَرْأَتَيْنِ اللَّتَيْنِ شَهِدَتَا رَجُلٌ وَلَا يَمِينٌ وَقَدْ يَكُونُ ذَلِكَ فِي الْأَمْوَالِ الْعِظَامِ مِنْ الذَّهَبِ وَالْوَرِقِ وَالرِّبَاعِ وَالْحَوَائِطِ وَالرَّقِيقِ وَمَا سِوَى ذَلِكَ مِنْ الْأَمْوَالِ وَلَوْ شَهِدَتْ امْرَأَتَانِ عَلَى دِرْهَمٍ وَاحِدٍ أَوْ أَقَلَّ مِنْ ذَلِكَ أَوْ أَكْثَرَ لَمْ تَقْطَعْ شَهَادَتُهُمَا شَيْئًا وَلَمْ تَجُزْ إِلَّا أَنْ يَكُونَ مَعَهُمَا شَاهِدٌ أَوْ يَمِينٌ قَالَ مَالِك وَمِنْ النَّاسِ مَنْ يَقُولُ لَا تَكُونُ الْيَمِينُ مَعَ الشَّاهِدِ الْوَاحِدِ وَيَحْتَجُّ بِقَوْلِ اللهِ تَبَارَكَ وَتَعَالَى وَقَوْلُهُ الْحَقُّ { وَاسْتَشْهِدُوا شَهِيدَيْنِ مِنْ رِجَالِكُمْ فَإِنْ لَمْ يَكُونَا رَجُلَيْنِ فَرَجُلٌ وَامْرَأَتَانِ مِمَّنْ تَرْضَوْنَ مِنْ الشُّهَدَاءِ } يَقُولُ فَإِنْ لَمْ يَأْتِ بِرَجُلٍ وَامْرَأَتَيْنِ فَلَا شَيْءَ لَهُ وَلَا يُحَلَّفُ مَعَ شَاهِدِهِ قَالَ مَالِك فَمِنْ الْحُجَّةِ عَلَى مَنْ قَالَ ذَلِكَ الْقَوْلَ أَنْ يُقَالَ لَهُ أَرَأَيْتَ لَوْ أَنَّ رَجُلًا ادَّعَى عَلَى رَجُلٍ مَالًا أَلَيْسَ يَحْلِفُ الْمَطْلُوبُ مَا ذَلِكَ الْحَقُّ عَلَيْهِ فَإِنْ حَلَفَ بَطَلَ ذَلِكَ عَنْهُ وَإِنْ نَكَلَ عَنْ الْيَمِينِ حُلِّفَ صَاحِبُ الْحَقِّ إِنَّ حَقَّهُ لَحَقٌّ وَثَبَتَ حَقُّهُ عَلَى صَاحِبِهِ فَهَذَا مَا لَا اخْتِلَافَ فِيهِ عِنْدَ أَحَدٍ مِنْ النَّاسِ وَلَا بِبَلَدٍ مِنْ الْبُلْدَانِ فَبِأَيِّ شَيْءٍ أَخَذَ هَذَا أَوْ فِي أَيِّ مَوْضِعٍ مِنْ كِتَابِ اللهِ وَجَدَهُ فَإِنْ أَقَرَّ بِهَذَا فَلْيُقْرِرْ بِالْيَمِينِ مَعَ الشَّاهِدِ وَإِنْ لَمْ يَكُنْ ذَلِكَ فِي كِتَابِ اللهِ عَزَّ وَجَلَّ وَأَنَّهُ لَيَكْفِي مِنْ ذَلِكَ مَا مَضَى مِنْ السُّنَّةِ وَلَكِنْ الْمَرْءُ قَدْ يُحِبُّ أَنْ يَعْرِفَ وَجْهَ الصَّوَابِ وَمَوْقِعَ الْحُجَّةِ فَفِي هَذَا بَيَانُ مَا أَشْكَلَ مِنْ ذَلِكَ إِنْ شَاءَ اللهُ تَعَالَى.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>আবূ সালামাহ্ ও সুলায়মান ইব্নু ইয়াসার (র)-কে জিজ্ঞেস করা হয়েছিল যে, সাক্ষী ও কসমের দ্বারা ফয়সালা করা যাবে কি? উত্তরে তাঁরা বললেন, হ্যাঁ। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) মালিক (র) বলেন যে, একজন সাক্ষীর সাথে বাঁদীর কসম গ্রহণের প্রথা পূর্ব হতে প্রচলিত হয়ে আসছে। সে যদি কসম করে তবে তার দাবি প্রমাণিত হবে। আর যদি সে কসম করতে ভয় পায় অথবা অস্বীকার করে তবে বিবাদীকে কসম দেয়া হবে। যদি বিবাদী কসম করে নেয় তবে ঐ হক (পাওনা) বিবাদীর উপর হতে এড়িয়ে যাবে। আর যদি সেও কসম করতে অস্বীকার করে তবে পুনরায় বাঁদীর দাবি তার উপর ন্যস্ত হবে। মালিক (র) বলেন যে, কসমসহ সাক্ষ্য শুধু মালের বেলায় চলবে, হুদুদ (শরীয়তের শাস্তি), বিবাহ, তালাক, গোলাম আযাদ, চুরি ও অপবাদের মধ্যে চলবে না। অতঃপর যদি কেউ বলে যে, গোলাম আযাদ মালের মধ্যে শামিল, তবে সে ভুল করবে। কারণ ব্যাপার অন্য রকম, যদি এমন হত যে, সে বলেছে তবে গোলাম একজন সাক্ষীসহ হাযির হলে কসম নিয়ে তাকে আযাদ করে দেয়া উচিত ছিল। আর যদি গোলাম একজন সাক্ষী আনে কোন মালের ব্যাপারে যে, সে মালিকের উপর দাবি করে তবে সেই ক্ষেত্রে একজন সাক্ষীসহ কসম নিতে হবে এবং তার হক প্রমাণিত হবে। যেমন আযাদ মানুষ হলফ করলে হয়। মালিক (র) বলেন আমাদের নিকট গ্রহণযোগ্য নিয়ম এই যে, গোলাম যদি তার আযাদ হওয়ার সপক্ষে একজন সাক্ষী নিয়ে আসে তবে তার মনিবকে কসম দেয়া হবে যে, তাহার গোলামকে আযাদ করেনি। তা হলেই গোলামের আযাদী প্রমাণিত হবে না। মালিক (র) বলেন যে, এই নিয়ম তালাকের ব্যাপারেও। যদি কোন স্ত্রী লোক তালাকের ব্যাপারে একজন সাক্ষী নিয়ে আসে তবে স্বামীকেও কসম করানো হবে। যদি স্বামী তালাক না দেয়ার উপর কসম করে তবে তালাক প্রমাণিত হবে না। মালিক (র) বলেন যে, এভাবেই তালাক ও আযাদ-এর সাক্ষ্যের মধ্যে এক সাক্ষী থাকলে স্বামী ও মনিবকে কসম করানো হবে। কেননা আযাদ করা (ই’তাক) একটি শরীয়তী সীমারেখার মধ্য হতে একটি, তার মধ্যে স্ত্রীলোকদের সাক্ষ্য জায়েয নেই। কেননা গোলাম আযাদ হয়ে গেলেই তার মর্যাদা প্রতিষ্ঠিত হয়ে যায় এবং তার কারণে শাস্তি অন্যের উপর পতিত হয় এবং অন্যের কারণে শাস্তি তার উপর পতিত হয়। সে যদি যিনা করে এবং বিবাহিত হয় তবে তাকে রজম (প্রস্তর নিক্ষেপ) করা হবে। আর যদি সে হত্যা করে তবে তার বদলায় তাকেও হত্যা করা হবে এবং তার ওয়ারিসগণ মীরাস দাবি করতে পারবে। কেউ যদি প্রশ্ন করে যে, যদি কোন মনিব তার গোলামকে আযাদ করে এবং কোন ব্যক্তি এসে গোলামের মনিবের নিকট নিজের কর্জ দাবি করে এবং তার সপক্ষে একজন পুরুষ ও দুইজন মহিলাকে সাক্ষীরূপে পেশ করে তবে মনিবের উপর করয প্রমাণিত হয়ে যাবে। আর যদি মনিবের নিকট এই গোলাম ছাড়া আর কোন সম্পদ না থাকে তবে গোলামের আযাদী ভঙ্গ হয়ে যাবে। এর দ্বারা প্রমাণিত হয় যে, আযাদীর ব্যাপারে মেয়েদের সাক্ষ্য গ্রহণযোগ্য। তার উত্তর এই যে, এখানে মেয়েদের সাক্ষ্য কর্জ প্রমাণের জন্য গ্রহণযোগ্য। গোলাম আযাদের ব্যাপারে নয়। তার উদাহরণ এইরূপ যে, যদি কোন লোক তার গোলামকে আযাদ করে দেয়, অতঃপর তার পাওনাদারগণ এক সাক্ষী ও কসমের দ্বারা নিজের দাবি প্রমাণিত করে এবং এর কারণে গোলামের আযাদী বাতিল করে দেয়া হবে। অথবা কেউ গোলামের মনিবের উপর কর্জের দাবি করে এবং সাক্ষী না থাকে তবে মনিব হতে কসম গ্রহণ করা হবে। যদি কসম করতে অস্বীকার করে তবে বাঁদীর নিকট হতে কসম নেয়া হবে এবং কর্জ মনিবের উপর প্রমাণিত হবে এবং গোলামের আযাদী বাতিল হবে। এমনিভাবে যদি কেউ কোন দাসীকে বিবাহ করে এবং দাসীর মনিব স্বামীকে বলে যে, তুমি এবং অমুক ব্যক্তি মিলে আমার অমুক দাসীকে এত টাকায় খরিদ করেছ। স্বামী সম্পূর্ণরূপে অস্বীকার করল। এদিকে মনিব যদি একজন পুরুষ ও দুইজন স্ত্রী লোক সাক্ষীরূপে পেশ করে তবে এই অবস্থাতে বিক্রয় প্রমাণিত হয়ে যাবে এবং সে হকদার হয়ে যাবে ও বিবাহ হারাম হয়ে যাবে এবং বিবাহ ভঙ্গ হয়ে যাবে। অথচ স্ত্রীলোকের সাক্ষ্য তালাকের ব্যাপারে জায়েয নেই। মালিক (র) বলেন এইরূপভাবে যদি কেউ কোন আযাদ লোকের প্রতি যিনার অপবাদ দেয় তবে তার উপর শরীয়তের হুদুদ (শাস্তি) আসবে। আর যদি একজন পুরুষ ও দুইজন স্ত্রীলোককে সাক্ষীরূপে আনে এবং তারা সাক্ষ্য দেয় যে, যার উপর অপবাদ দেয়া হচ্ছে সে গোলাম তবে অপবাদ কারীর উপর হতে শাস্তি বাতিল হয়ে যাবে। অথচ স্ত্রীলোকদের সাক্ষ্য অপবাদের মধ্যে চলে না। মালিক (র) বলেন যে, যার মধ্যে বিচার ভিন্নরূপ হয় তার উদাহরণ এইরূপ- যেমন দুইজন স্ত্রীলোক সাক্ষ্য দিল যে, এই বাচ্চা জীবিত অবস্থায় ভূমিষ্ঠ হয়েছে, তা হলে এই বাচ্চার জন্য মীরাস প্রমাণিত হবে এবং এই সন্তানের উত্তরাধিকার যে সেই মীরাসের মালিক হবে, যদি সন্তান মৃত্যুবরণ করে এইখানেও দুইজন স্ত্রীলোকের সাথে কোন পুরুষ নেই কিংবা কসমও নেই। কোন সময় মীরাসের মাল অনেক হয়ে থাকে, যেমন স্বর্ণ, রৌপ্য, জমি, বাগান, গোলাম, ইহা ছাড়া অন্যান্য সম্পদ আর যদি একটি দিরহাম অথবা তার চাইতেও কম বা অধিক মালের ব্যাপারে দুইজন স্ত্রীলোক সাক্ষ্য প্রদান করে তবে তাদের সাক্ষ্যের দ্বারা কোন পরিবর্তন হবে না এবং কার্যকরীও হবে না, যতক্ষণ তাদের সাথে একজন পুরুষ সাক্ষ্য না থাকবে অথবা কসম না থাকবে। মালিক (র) বলেন যে, কোন কোন লোক বলে যে, একজন সাক্ষীর সাথে কসম প্রয়োজন হয় না এবং দলীলস্বরূপ এই আয়াত পেশ করে, “আল্লাহর কথা সত্য যদি দুইজন পুরুষ না পাওয়া যায় তবে একজন পুরুষ ও দুইজন স্ত্রীলোককে, যারা তোমাদের মনঃপূত হয় সাক্ষী মনোনীত কর।” (সূরা বাক্বারাহ, আয়াত ২৮২) তারা বলে যে, একজন পুরুষ ও দুইজন স্ত্রীলোক না হলে তাদের জন্য কিছুই নেই। একজন সাক্ষীর সঙ্গে কসমও গ্রহণ করা হয় না। মালিক (র) উত্তরে বলেন যারা এরূপ বলে, তাদের বলা হবে যে, তুমি কি দেখ না যে যদি কেউ কারো নিকট অর্থ দাবি করে তবে বিবাদীর নিকট হতে কি কসম নেয়া হয় না? যদি সে কসম করে তবে তার উপর দাবিকৃত হক বাতিল হয়ে যায়। আর যদি সে কসম করতে অস্বীকার করে তবে দাবিদারকে কসম দেয়া হবে যে, তার দাবি সত্য, তা হলে হক তার উপর অবধারিত হয়ে যাবে। এই মাসআলায় কোন মানুষের মতভেদ নেই, আর কোন দেশের লোকেরও এতে মতভেদ নেই। তবে তোমরা এই কথা কোথা হতে এনেছ? এবং আল্লাহর কোন কিতাব হতে সংগ্রহ করেছ? যদি তোমাদের নিকট এটা জায়েয থাকে তবে একজন সাক্ষীর সাথে কসমের কথাও স্বীকার যথেষ্ট, কিন্তু যদি সত্য কথা পাওয়া যায় তা মেনে নেয়া কর্তব্য এবং দলীলের বিষয়গুলো দেখা প্রয়োজন। আল্লাহ্‌র ইচ্ছায় কঠিন বিষয় সহজ হয়ে যাবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>قَالَ يَحْيَى قَالَ مَالِك عَنْ جَمِيلِ بْنِ عَبْدِ الرَّحْمَنِ الْمُؤَذِّنِ أَنَّهُ كَانَ يَحْضُرُ عُمَرَ بْنَ عَبْدِ الْعَزِيْزِ وَهُوَ يَقْضِي بَيْنَ النَّاسِ فَإِذَا جَاءَهُ الرَّجُلُ يَدَّعِي عَلَى الرَّجُلِ حَقًّا نَظَرَ فَإِنْ كَانَتْ بَيْنَهُمَا مُخَالَطَةٌ أَوْ مُلَابَسَةٌ أَحْلَفَ الَّذِي ادُّعِيَ عَلَيْهِ وَإِنْ لَمْ يَكُنْ شَيْءٌ مِنْ ذَلِكَ لَمْ يُحَلِّفْهُ قَالَ مَالِك وَعَلَى ذَلِكَ الْأَمْرُ عِنْدَنَا أَنَّهُ مَنْ ادَّعَى عَلَى رَجُلٍ بِدَعْوَى نُظِرَ فَإِنْ كَانَتْ بَيْنَهُمَا مُخَالَطَةٌ أَوْ مُلَابَسَةٌ أُحْلِفَ الْمُدَّعَى عَلَيْهِ فَإِنْ حَلَفَ بَطَلَ ذَلِكَ الْحَقُّ عَنْهُ وَإِنْ أَبَى أَنْ يَحْلِفَ وَرَدَّ الْيَمِينَ عَلَى الْمُدَّعِي فَحَلَفَ طَالِبُ الْحَقِّ أَخَذَ حَقَّهُ.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>জামিল ইব্নু আবদির রহমান (র) উমার ইব্নু আবদুল আযীয (র)-এর দরবারে হাযির হয়ে তাঁর বিচার কার্য দেখতেন। কোন লোক যদি কারো প্রতি কোন দাবি করত তবে এর প্রতি খুব লক্ষ্য করে দেখতেন। অতঃপর যদি বলতেন যে, তাদের মধ্যে (বাদী-বিবাদী) কাজে-কারবারে সমতা ও সামঞ্জস্য আছে, তবে বিবাদীকে কসম করাতেন, না হয় কসম করাতেন না। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) মালিক (র) বলেন যে, আমাদের কাছেও এই প্রথা যে, যদি কেউ কারো প্রতি কিছু দাবি করে তবে দেখতে হবে যে, যদি বাদী ও বিবাদীর মধ্যে সম্পর্ক ভাল থাকে এবং তারা সমপর্যায়ের হয় তবে বিবাদীকে কসম করাতে হবে। যদি সে কসম করে তবে বাদীর দাবি বিবাদী হতে ছুটে যাবে। আর যদি বিবাদী কসম করতে অস্বীকার করে তবে এই কসম বাদীর দিকে ফিরে আসবে। সুতরাং সেই অবস্থায় কসম করে তার দাবি প্রমাণিত করে আদায় করে নিবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>قَالَ يَحْيَى قَالَ مَالِك عَنْ هِشَامِ بْنِ عُرْوَةَ أَنَّ عَبْدَ اللهِ بْنَ الزُّبَيْرِ كَانَ يَقْضِي بِشَهَادَةِ الصِّبْيَانِ فِيمَا بَيْنَهُمْ مِنْ الْجِرَاحِ. قَالَ مَالِك الْأَمْرُ الْمُجْتَمَعُ عَلَيْهِ عِنْدَنَا أَنَّ شَهَادَةَ الصِّبْيَانِ تَجُوزُ فِيمَا بَيْنَهُمْ مِنْ الْجِرَاحِ وَلَا تَجُوزُ عَلَى غَيْرِهِمْ وَإِنَّمَا تَجُوزُ شَهَادَتُهُمْ فِيمَا بَيْنَهُمْ مِنْ الْجِرَاحِ وَحْدَهَا لَا تَجُوزُ فِي غَيْرِ ذَلِكَ إِذَا كَانَ ذَلِكَ قَبْلَ أَنْ يَتَفَرَّقُوا أَوْ يُخَبَّبُوا أَوْ يُعَلَّمُوا فَإِنْ افْتَرَقُوا فَلَا شَهَادَةَ لَهُمْ إِلَّا أَنْ يَكُونُوا قَدْ أَشْهَدُوا الْعُدُولَ عَلَى شَهَادَتِهِمْ قَبْلَ أَنْ يَفْتَرِقُوا.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>আবদুল্লাহ্ ইব্নু যুবায়র (রা) বালকদের সাক্ষ্যের উপর ভিত্তি করে তাদের মারামারির বিচার করে দিতেন। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) মালিক (র) বলেন আমাদের নিকট এই হুকুম যে, যদি বালকগণ একে অপরকে আহত করে দেয় তবে তাদের সাক্ষ্য বৈধ। এটা ছাড়া অন্য মামলায় তা বৈধ হবে না। ইহা ঐ সময় হবে যখন ঝগড়া করে সেখানেই থাকে, অন্যত্র না গিয়ে থাকে। যদি অন্যত্র চলে যায় তবে তাদের সাক্ষ্য জায়েয নয়। যতক্ষণ না কোন নির্ভরযোগ্য মানুষের সাক্ষ্য গ্রহণ করা হয় এবং বালকগণও ঐখানেই থাকে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>قَالَ يَحْيَى قَالَ مَالِك عَنْ دَاوُدَ بْنِ الْحُصَيْنِ أَنَّهُ سَمِعَ أَبَا غَطَفَانَ بْنَ طَرِيفٍ الْمُرِّيَّ يَقُولُ اخْتَصَمَ زَيْدُ بْنُ ثَابِتٍ الْأَنْصَارِيُّ وَابْنُ مُطِيعٍ فِي دَارٍ كَانَتْ بَيْنَهُمَا إِلَى مَرْوَانَ بْنِ الْحَكَمِ وَهُوَ أَمِيرٌ عَلَى الْمَدِينَةِ فَقَضَى مَرْوَانُ عَلَى زَيْدِ بْنِ ثَابِتٍ بِالْيَمِينِ عَلَى الْمِنْبَر. فَقَالَ زَيْدُ بْنُ ثَابِتٍ أَحْلِفُ لَهُ مَكَانِي قَالَ فَقَالَ مَرْوَانُ لَا وَاللهِ إِلَّا عِنْدَ مَقَاطِعِ الْحُقُوقِ قَالَ فَجَعَلَ زَيْدُ بْنُ ثَابِتٍ يَحْلِفُ أَنَّ حَقَّهُ لَحَقٌّ وَيَأْبَى أَنْ يَحْلِفَ عَلَى الْمِنْبَرِ قَالَ فَجَعَلَ مَرْوَانُ بْنُ الْحَكَمِ يَعْجَبُ مِنْ ذَلِكَ. ২৬৯৬-قَالَ مَالِك لَا أَرَى أَنْ يُحَلَّفَ أَحَدٌ عَلَى الْمِنْبَرِ عَلَى أَقَلَّ مِنْ رُبُعِ دِينَارٍ وَذَلِكَ ثَلَاثَةُ دَرَاهِمَ ِِِِ.</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>যায়দ ইব্নু সাবিত (রা) ও ইব্নু মুতী-এর মধ্যে একটি ঘরের ব্যাপারে ঝগড়া হয়ে যায়। অবশেষে তারা এর বিচার মারওয়ানের নিকট নিয়ে গেলেন। সেই সময় তিনি মদীনার শাসনকর্তা ছিলেন। মারওয়ান বললেন, যায়দ ইব্নু সাবিত মিম্বরের উপর উঠে কসম করে নিক। যায়দ (রা) বললেন, আমি আমার স্থানে দাঁড়িয়ে কসম করে নেই। মারওয়ান বললেন, আল্লাহর কসম, এটা হতে পারে না। অন্য লোকেরা যেখানে তাদের হকের মীমাংসা করে সেখানেই করতে হবে। অতঃপর যায়দ (রা) নিজ স্থানে দাঁড়িয়ে বলতে লাগলেন, আমি কসম করে বলছি যে, আমার দাবি সত্য, কিন্তু মিম্বরের উপর গিয়ে কসম করতে অস্বীকার করতে লাগলেন। মারওয়ান এতে বিস্মিত হয়ে গেলেন। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) মালিক (র) বলেন যে, এক-চতুর্থাংশ দীনারের কম দাবি হলে মিম্বরের উপর কাউকে কসম করানো ঠিক নয়, এক চতুর্থাংশ দীনারের মূল্য হল তিন দিরহাম।</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>قَالَ يَحْيَى حَدَّثَنَا مَالِك عَنْ ابْنِ شِهَابٍ عَنْ سَعِيدِ بْنِ الْمُسَيَّبِ أَنَّ رَسُولَ اللهِ صَلَّى اللهُ عَلَيْهِ وَسَلَّمَ قَالَ لَا يَغْلَقُ الرَّهْنُ قَالَ مَالِك وَتَفْسِيرُ ذَلِكَ فِيمَا نُرَى وَاللهُ أَعْلَمُ أَنْ يَرْهَنَ الرَّجُلُ الرَّهْنَ عِنْدَ الرَّجُلِ بِالشَّيْءِ وَفِي الرَّهْنِ فَضْلٌ عَمَّا رُهِنَ بِهِ فَيَقُولُ الرَّاهِنُ لِلْمُرْتَهِنِ إِنْ جِئْتُكَ بِحَقِّكَ إِلَى أَجَلٍ يُسَمِّيهِ لَهُ وَإِلَّا فَالرَّهْنُ لَكَ بِمَا رُهِنَ فِيهِ قَالَ فَهَذَا لَا يَصْلُحُ وَلَا يَحِلُّ وَهَذَا الَّذِي نُهِيَ عَنْهُ وَإِنْ جَاءَ صَاحِبُهُ بِالَّذِي رَهَنَ بِهِ بَعْدَ الْأَجَلِ فَهُوَ لَهُ وَأُرَى هَذَا الشَّرْطَ مُنْفَسِخًا.</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>রসূলুল্লাহ্ সল্লাল্লাহু আলাইহি ওয়াসাল্লাম বলেছেন “রেহেনকে (বন্ধক) বন্ধ করা উচিত নয়।” (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) মালিক (র) বলেন, এর ব্যাখ্যা আমাদের নিকট এই যে, (আল্লাহই ভাল জানেন) এক ব্যক্তি কিছু জিনিস অপর ব্যক্তির নিকট রেহেন রাখল কোন জিনিসের পরিবর্তে। আর রেহেন-এর বস্তুটি মূল্যবান যে জিনিসের পরিবর্তে রাখা হয়েছে তার চাইতে। অতঃপর রেহেন (গচ্ছিতকারী) মুরতাহেনকে (যার কাছে রাখা হয়েছে) বলল, আমি যদি নির্দিষ্ট তারিখে আপনার জিনিস নিয়ে আসি তবে আমার জিনিস আমাকে দিবেন আর যদি আমি এ সময় না আসতে পারি তবে গচ্ছিত মাল আপনার। এইরূপ করা জায়েয নাই এবং হালালও নয়। এটাই নিষিদ্ধ করা হয়েছে। যদি নির্দিষ্ট দিনের পরে ঐ ব্যক্তি আসে তবে রেহেনের বস্তু তারই হবে। আর এই শর্ত বাতিল হবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1409</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي مَالِك عَنْ ابْنِ شِهَابٍ أَنَّ عَبْدَ الْمَلِكِ بْنَ مَرْوَانَ قَضَى فِي امْرَأَةٍ أُصِيبَتْ مُسْتَكْرَهَةً بِصَدَاقِهَا عَلَى مَنْ فَعَلَ ذَلِكَ بِهَاُ. قَالَ يَحْيَى سَمِعْت مَا لِكًا يَقُولُ الْأَمْرُ عِنْدَنَا فِي الرَّجُلِ يَغْتَصِبُ الْمَرْأَةَ بِكْرًا كَانَتْ أَوْ ثَيِّبًا إِنَّهَا إِنْ كَانَتْ حُرَّةً فَعَلَيْهِ صَدَاقُ مِثْلِهَا وَإِنْ كَانَتْ أَمَةً فَعَلَيْهِ مَا نَقَصَ مِنْ ثَمَنِهَا وَالْعُقُوبَةُ فِي ذَلِكَ عَلَى الْمُغْتَصِبِ وَلَا عُقُوبَةَ عَلَى الْمُغْتَصَبَةِ فِي ذَلِكَ كُلِّهِ وَإِنْ كَانَ الْمُغْتَصِبُ عَبْدًا فَذَلِكَ عَلَى سَيِّدِهِ إِلَّا أَنْ يَشَاءَ أَنْ يُسَلِّمَهُ.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>আবদুল মালিক ইব্নু মারওয়ান জবরদস্তিভাবে যিনা করা হয়েছে এমন স্ত্রীলোকের ফয়সালা এই দিয়েছেন ব্যভিচার যে করেছে ঐ স্ত্রীলোকটিকে মোহর দান করবে। মালিক (র) বলেন আমাদের নিকট এই ফয়সালা যে, যদি কেউ কোন স্ত্রীলোকের উপর জবরদস্তি করে, চাই সে কুমারী হোক অথবা অকুমারী, যদি সে স্বাধীনা হয় তবে তাকে মাহরে মিসাল দেয়া আবশ্যক। আর যদি সে দাসী হয় তবে যিনার দ্বারা যে মূল্য কম হয়েছে তা আদায় করতে হবে এবং ব্যভিচারীর শাস্তিও সঙ্গে সঙ্গে হবে এবং উক্ত স্ত্রীলোকের উপর কোন শাস্তি হবে না। আর যদি ব্যভিচারী গোলাম হয় তবে মনিবের জরিমানা দিতে হবে। কিন্তু যদি গোলামকে ক্ষতিপূরণ হিসাবে দিয়ে দেয় তবে ভিন্ন কথা। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>قَالَ يَحْيَى قَالَ مَالِك عَنْ ابْنِ شِهَابٍ عَنْ سُنَيْنٍ أَبِي جَمِيلَةَ رَجُلٌ مِنْ بَنِي سُلَيْمٍ أَنَّهُ وَجَدَ مَنْبُوذًا فِي زَمَانِ عُمَرَ بْنِ الْخَطَّابِ قَالَ فَجِئْتُ بِهِ إِلَى عُمَرَ بْنِ الْخَطَّابِ فَقَالَ مَا حَمَلَكَ عَلَى أَخْذِ هَذِهِ النَّسَمَةِ فَقَالَ وَجَدْتُهَا ضَائِعَةً فَأَخَذْتُهَا فَقَالَ لَهُ عَرِيفُهُ يَا أَمِيرَ الْمُؤْمِنِينَ إِنَّهُ رَجُلٌ صَالِحٌ فَقَالَ لَهُ عُمَرُ أَكَذَلِكَ قَالَ نَعَمْ فَقَالَ عُمَرُ بْنُ الْخَطَّابِ اذْهَبْ فَهُوَ حُرٌّ وَلَكَ وَلَاؤُهُ وَعَلَيْنَا نَفَقَتُهُ. قَالَ يَحْيَى سَمِعْت مَا لِكًا يَقُولُ الْأَمْرُ عِنْدَنَا فِي الْمَنْبُوذِ أَنَّهُ حُرٌّ وَأَنَّ وَلَاءَهُ لِلْمُسْلِمِينَ هُمْ يَرِثُونَهُ وَيَعْقِلُونَ عَنْهُ.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>সুনাইন ইব্নু আবী জমিলা (র) বনী সুলায়মান বংশোদ্ভূত, তিনি উমার (রা)-এর জামানায় ফেলে দেয়া একটি শিশু পেয়েছিলেন। তিনি বলেন যে, তাকে আমি উঠিয়ে উমার (রা)-এর দরবারে হাযির হলাম। উমার (রা) বললেন, তুমি তাকে কেন উঠিয়েছ? তিনি বললেন, আমি তাকে উঠিয়ে না আনলে সে ধ্বংস হয়ে যেত। এমন সময় পরিচিত এক ব্যক্তি বলল, হে আমিরুল মু‘মিনীন, আমি এই ব্যক্তিকে চিনি, সে খুব নেককার লোক। উমার (রা) বললেন, সত্যই কি সে নেককার? সে বলল, হ্যাঁ। অতঃপর উমার (রা) বললেন, তুমি চলে যাও, এই সন্তান আযাদ (মুক্ত), তুমি তার অভিভাবকত্ব পাবে। আর আমরা তার খরচাদি বহন করব। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) মালিক (র) বলেন আমাদের নিকট হারানো প্রাপ্ত সন্তান আযাদ। তার অভিভাবকত্ব মুসলমানদের জন্য, তারাই তার উত্তরাধিকারী এবং তারাই তার পক্ষ হতে দীয়্যত (ক্ষতিপূরণ) দেবে।</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي مَالِك عَنْ يَزِيدَ بْنِ عَبْدِ اللهِ بْنِ الْهَادِي عَنْ مُحَمَّدِ بْنِ إِبْرَاهِيمَ بْنِ الْحَارِثِ التَّيْمِيِّ عَنْ سُلَيْمَانَ بْنِ يَسَارٍ عَنْ عَبْدِ اللهِ بْنِ أَبِي أُمَيَّةَ أَنَّ امْرَأَةً هَلَكَ عَنْهَا زَوْجُهَا فَاعْتَدَّتْ أَرْبَعَةَ أَشْهُرٍ وَعَشْرًا ثُمَّ تَزَوَّجَتْ حِينَ حَلَّتْ فَمَكَثَتْ عِنْدَ زَوْجِهَا أَرْبَعَةَ أَشْهُرٍ وَنِصْفَ شَهْرٍ ثُمَّ وَلَدَتْ وَلَدًا تَامًّا فَجَاءَ زَوْجُهَا إِلَى عُمَرَ بْنِ الْخَطَّابِ فَذَكَرَ ذَلِكَ لَهُ فَدَعَا عُمَرُ نِسْوَةً مِنْ نِسَاءِ الْجَاهِلِيَّةِ قُدَمَاءَ فَسَأَلَهُنَّ عَنْ ذَلِكَ فَقَالَتْ امْرَأَةٌ مِنْهُنَّ أَنَا أُخْبِرُكَ عَنْ هَذِهِ الْمَرْأَةِ هَلَكَ عَنْهَا زَوْجُهَا حِينَ حَمَلَتْ مِنْهُ فَأُهْرِيقَتْ عَلَيْهِ الدِّمَاءُ فَحَشَّ وَلَدُهَا فِي بَطْنِهَا فَلَمَّا أَصَابَهَا زَوْجُهَا الَّذِي نَكَحَهَا وَأَصَابَ الْوَلَدَ الْمَاءُ تَحَرَّكَ الْوَلَدُ فِي بَطْنِهَا وَكَبِرَ فَصَدَّقَهَا عُمَرُ بْنُ الْخَطَّابِ وَفَرَّقَ بَيْنَهُمَا وَقَالَ عُمَرُ أَمَا إِنَّهُ لَمْ يَبْلُغْنِي عَنْكُمَا إِلَّا خَيْرٌ وَأَلْحَقَ الْوَلَدَ بِالْأَوَّلِ.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>এক স্ত্রীলোকের স্বামীর ইন্তেকাল হয়। অতঃপর চার মাস দশ দিন ইদ্দত পালন করার পর অন্য একজনের নিকট তার বিবাহ হয়। বিবাহের পর সেই স্বামীর নিকট সাড়ে চার মাস অতিবাহিত করার পর তার একটি পূর্ণাঙ্গ সন্তান ভূমিষ্ঠ হল। অতঃপর তার স্বামী উমার (রা)-এর নিকট এসে সমস্ত ঘটনা বর্ণনা করল। উমার (রা) অন্ধকার যুগের কয়েকজন বৃদ্ধা স্ত্রীলোককে ডাকালেন এবং তাদেরকে এই সম্বন্ধে প্রশ্ন করলেন। তখন তাদের একজন বলল, আমি আপনাকে তার বৃত্তান্ত বলিতেছি। এই স্ত্রীলোকটি তার মৃত স্বামী হতে গর্ভবতী হয়েছিল। সন্তান গর্ভে থাকা অবস্থায় তার রক্তস্রাব হল, এতে সন্তান শুকিয়ে যায়। অতঃপর দ্বিতীয় বিবাহের পর স্বামী তার সাথে সংগত হওয়ায় সন্তানের উপর পুরুষের বীর্য পতিত হয়। এতে সন্তান নড়াচড়া করে এবং বড় হতে থাকে। অতঃপর উমার (রা) তাদের কথা সত্য বলে মানলেন এবং বিবাহ ভঙ্গ করে দিলেন এবং বললেন যে, তোমাদের সম্বন্ধে কোন খারাপ কথা আমি শুনিনি। অতঃপর সন্তানটি প্রথম স্বামীর ঔরসজাত বলে সিদ্ধান্ত দিলেন। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1417</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي مَالِك عَنْ يَحْيَى بْنِ سَعِيدٍ عَنْ سُلَيْمَانَ بْنِ يَسَارٍ أَنَّ عُمَرَ بْنَ الْخَطَّابِ كَانَ يُلِيطُ أَوْلَادَ الْجَاهِلِيَّةِ بِمَنْ ادَّعَاهُمْ فِي الْإِسْلَامِ فَأَتَى رَجُلَانِ كِلَاهُمَا يَدَّعِي وَلَدَ امْرَأَةٍ فَدَعَا عُمَرُ بْنُ الْخَطَّابِ قَائِفًا فَنَظَرَ إِلَيْهِمَا فَقَالَ الْقَائِفُ لَقَدْ اشْتَرَكَا فِيهِ فَضَرَبَهُ عُمَرُ بْنُ الْخَطَّابِ بِالدِّرَّةِ ثُمَّ دَعَا الْمَرْأَةَ فَقَالَ أَخْبِرِينِي خَبَرَكِ فَقَالَتْ كَانَ هَذَا لِأَحَدِ الرَّجُلَيْنِ يَأْتِينِي وَهِيَ فِي إِبِلٍ لِأَهْلِهَا فَلَا يُفَارِقُهَا حَتَّى يَظُنَّ وَتَظُنَّ أَنَّهُ قَدْ اسْتَمَرَّ بِهَا حَبَلٌ ثُمَّ انْصَرَفَ عَنْهَا فَأُهْرِيقَتْ عَلَيْهِ دِمَاءٌ ثُمَّ خَلَفَ عَلَيْهَا هَذَا تَعْنِي الْآخَرَ فَلَا أَدْرِي مِنْ أَيِّهِمَا هُوَ قَالَ فَكَبَّرَ الْقَائِفُ فَقَالَ عُمَرُ لِلْغُلَامِ وَالِ أَيَّهُمَا شِئْتَ.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>উমার (রা) অন্ধকার যুগের সন্তানকে যদি কেউ ইসলামের যুগে দাবি করত তবে তার সাথে মিলিয়ে দিতেন। একবার দুইজন লোক একটি সন্তানকে নিজের বলে দাবি করে। অতঃপর উমার (রা) কেয়াফাবিদকে (লক্ষণ দেখে পরিচয় নির্ণয়কারী) ডেকে পাঠালেন। কেয়াফাবিশারদ সন্তানকে দেখে বলল, সন্তান দুইজনেরই। অতঃপর উমার (রা) তাকে দোররা দ্বারা আঘাত করলেন। তার পর সন্তানের মাতাকে ডেকে বললেন তোমার বৃত্তান্ত খুলে বল। সে একজনের দিকে ঈঙ্গিত করে বলল যে, সে আমার নিকট আসা-যাওয়া করত এবং আমি আমার বাড়ির উটের ঘরের কাছে থাকতাম। ঐ সময়ে সে আমার সথে সঙ্গম করত। অতঃপর সে যখন ধারণা করতে পারল যে, আমি গর্ভবতী হয়েছি তখন সে আর কাছে আসত না, আর আমার রক্তস্রাব দেখা যেত। তারপর এই দ্বিতীয়জন তার পর আমার নিকট এল। সেও আমার সাথে সঙ্গম করল। এখন আমি জানি না, এই সন্তান দুইজনের মধ্য হতে কার। ইহা শুনে কেয়াফাবিদ খুশিতে আল্লাহু আকবর (আল্লাহ্ মহান) বলে উঠল। অতঃপর উমার (রা) সন্তানকে বললেন, যার সাথে খুশি তুমি যেতে পার। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي مَالِك أَنَّهُ بَلَغَهُ أَنَّ عُمَرَ بْنَ الْخَطَّابِ أَوْ عُثْمَانَ بْنَ عَفَّانَ قَضَى أَحَدُهُمَا فِي امْرَأَةٍ غَرَّتْ رَجُلًا بِنَفْسِهَا وَذَكَرَتْ أَنَّهَا حُرَّةٌ فَتَزَوَّجَهَا فَوَلَدَتْ لَهُ أَوْلَادًا فَقَضَى أَنْ يَفْدِيَ وَلَدَهُ بِمِثْلِهِمْ. قَالَ يَحْيَى سَمِعْت مَا لِكًا يَقُولُ وَالْقِيمَةُ أَعْدَلُ فِي هَذَا إِنْ شَاءَ اللهُ.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>উমার (রা) অথবা উসমান (রা) এই দুইজনের মধ্যে একজন এক স্ত্রীলোকের ফয়সালা করেছিলেন। সেই স্ত্রীলোকটি ধোঁকা দিয়ে একজনকে বলল, আমি আযাদ এবং তার সাথে বিবাহ বন্ধনে আবদ্ধ হল। অতঃপর তাদের সন্তান হয়েছিল। ফয়সালা দেয়া হয়েছিল, স্বামী তার সন্তানের মতো বালক-বালিকা স্ত্রীলোকটির মনিবকে দিবে এবং নিজের সন্তান মুক্ত করে নিবে। মালিক (র) বলেন, এই স্থানে মূল্য দান করিয়া দেয়াই উত্তম। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>قَالَ يَحْيَى قَالَ مَالِك عَنْ ابْنِ شِهَابٍ عَنْ سَالِمِ بْنِ عَبْدِ اللهِ بْنِ عُمَرَ عَنْ أَبِيهِ أَنَّ عُمَرَ بْنَ الْخَطَّابِ قَالَ: مَا بَالُ رِجَالٍ يَطَئُونَ وَلَائِدَهُمْ ثُمَّ يَعْزِلُوهُنَّ لَا تَأْتِينِي وَلِيْدَةٌ يَعْتَرِفُ سَيِّدُهَا أَنْ قَدْ أَلَمَّ بِهَا إِلَّا أَلْحَقْتُ بِهِ وَلَدَهَا فَاعْزِلُوا بَعْدُ أَوْ اتْرُكُوْا.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>উমার (রা) বলেন যে, লোকদের হল কি, তারা দাসীদের সাথে সহবাস করে এবং আযল [১] করে। ভবিষ্যতে যদি কোন দাসী আমার নিকট আসে এবং তার মনিব তার সাথে সঙ্গম করার স্বীকারোক্তি করে তবে আমি ঐ সন্তানকে মনিবের সাথে মিলিত করে দিব, এখন তোমরা চাই আযল কর, চাই আযল না কর। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي مَالِك عَنْ نَافِعٍ عَنْ صَفِيَّةَ بِنْتِ أَبِي عُبَيْدٍ أَنَّهَا أَخْبَرَتْهُ أَنَّ عُمَرَ بْنَ الْخَطَّابِ قَالَ مَا بَالُ رِجَالٍ يَطَئُونَ وَلَائِدَهُمْ ثُمَّ يَدَعُوهُنَّ يَخْرُجْنَ لَا تَأْتِينِي وَلِيدَةٌ يَعْتَرِفُ سَيِّدُهَا أَنْ قَدْ أَلَمَّ بِهَا إِلَّا قَدْ أَلْحَقْتُ بِهِ وَلَدَهَا فَأَرْسِلُوهُنَّ بَعْدُ أَوْ أَمْسِكُوهُنَّ.২৭৪৮-قَالَ يَحْيَى سَمِعْت مَا لِكًا يَقُولُ الْأَمْرُ عِنْدَنَا فِي أُمِّ الْوَلَدِ إِذَا جَنَتْ جِنَايَةً ضَمِنَ سَيِّدُهَا مَا بَيْنَهَا وَبَيْنَ قِيمَتِهَا وَلَيْسَ لَهُ أَنْ يُسَلِّمَهَا وَلَيْسَ عَلَيْهِ أَنْ يَحْمِلَ مِنْ جِنَايَتِهَا أَكْثَرَ مِنْ قِيمَتِهَا.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>উমার (রা) বলেন, মানুষের হল কি? তারা দাসীদের সাথে সহবাস করে। অতঃপর তাকে ছেড়ে দেয়। এখন হতে যদি এমন কোন দাসী আমার নিকট আসে যার মনিব তার সাথে সঙ্গম করার স্বীকারোক্তি করে তবে সন্তানের বংশ তার সাথে জুড়ে দিব। এখন তোমরা তাকে ছেড়ে দাও, চাই রেখে দাও। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) মালিক (র) বলেন এই ব্যাপারে আমার মত এই যে, যদি কোন দাসী ক্ষতিকর কার্য করে তবে তার ক্ষতিপূরণ তার মনিব আদায় করবে। দাসীকে ক্ষতির পরিবর্তে দেয়া যাবে না। কিন্তু যদি জরিমানা তার মূল্যের চাইতে বেশি হয় তবে তা ভিন্ন কথা।</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي مَالِك عَنْ يَحْيَى بْنِ سَعِيدٍ أَنَّ سُلَيْمَانَ بْنَ يَسَارٍ أَخْبَرَهُ أَنَّ عَبْدَ اللهِ بْنَ عَيَّاشِ بْنِ أَبِي رَبِيعَةَ الْمَخْزُومِيَّ قَالَ أَمَرَنِي عُمَرُ بْنُ الْخَطَّابِ فِي فِتْيَةٍ مِنْ قُرَيْشٍ فَجَلَدْنَا وَلَائِدَ مِنْ وَلَائِدِ الْإِمَارَةِ خَمْسِينَ خَمْسِينَ فِي الزِّنَا</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>উমার ইব্নু খাত্তাব (রা) আমাকে এবং আরও কতিপয় কুরাইশী যুবককে ব্যভিচারের দায়ে প্রহার করতে আদেশ দিলে আমরা ব্যভিচারের শাস্তি হিসাবে বায়তুলমালের দাসীদেরকে পঞ্চাশ পঞ্চাশ বেত্রাঘাত করতাম। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي مَالِك عَنْ أَبِي الزِّنَادِ أَنَّهُ قَالَ جَلَدَ عُمَرُ بْنُ عَبْدِ الْعَزِيزِ عَبْدًا فِي فِرْيَةٍ ثَمَانِينَ قَالَ أَبُو الزِّنَادِ فَسَأَلْتُ عَبْدَ اللهِ بْنَ عَامِرِ بْنِ رَبِيعَةَ عَنْ ذَلِكَ فَقَالَ أَدْرَكْتُ عُمَرَ بْنَ الْخَطَّابِ وَعُثْمَانَ بْنَ عَفَّانَ وَالْخُلَفَاءَ هَلُمَّ جَرًّا فَمَا رَأَيْتُ أَحَدًا جَلَدَ عَبْدًا فِي فِرْيَةٍ أَكْثَرَ مِنْ أَرْبَعِينَ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>উমার ইব্নু আবদুল আযীয (র) এক দাসকে অপবাদের শাস্তি হিসাবে আশিটি বেত্রাঘাত করেছিলেন। আবূ যিনাদ বলেন, আমি আবদুল্লাহ্ ইব্নু ‘আমির (রা)-কে এ বিষয়ে জিজ্ঞেস করলাম। তিনি বললেন, আমি উমার ও উসমান (রা)-কে এবং তাদের পর অপর দুই খলীফাকে দেখেছি, কেউই কোন দাসকে অপবাদের শাস্তি হিসেবে চল্লিশ বেত্রাঘাতের বেশি মারেননি। [১] (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي مَالِك عَنْ زُرَيْقِ بْنِ حَكِيمٍ الْأَيْلِيِّ أَنَّ رَجُلًا يُقَالُ لَهُ مِصْبَاحٌ اسْتَعَانَ ابْنًا لَهُ فَكَأَنَّهُ اسْتَبْطَأَهُ فَلَمَّا جَاءَهُ قَالَ لَهُ يَا زَانٍ قَالَ زُرَيْقٌ فَاسْتَعْدَانِي عَلَيْهِ فَلَمَّا أَرَدْتُ أَنْ أَجْلِدَهُ قَالَ ابْنُهُ وَاللهِ لَئِنْ جَلَدْتَهُ لَأَبُوءَنَّ عَلَى نَفْسِي بِالزِّنَا فَلَمَّا قَالَ ذَلِكَ أَشْكَلَ عَلَيَّ أَمْرُهُ فَكَتَبْتُ فِيهِ إِلَى عُمَرَ بْنِ عَبْدِ الْعَزِيزِ وَهُوَ الْوَالِي يَوْمَئِذٍ أَذْكُرُ لَهُ ذَلِكَ فَكَتَبَ إِلَيَّ عُمَرُ أَنْ أَجِزْ عَفْوَهُ قَالَ زُرَيْقٌ وَكَتَبْتُ إِلَى عُمَرَ بْنِ عَبْدِ الْعَزِيزِ أَيْضًا أَرَأَيْتَ رَجُلًا افْتُرِيَ عَلَيْهِ أَوْ عَلَى أَبَوَيْهِ وَقَدْ هَلَكَا أَوْ أَحَدُهُمَا قَالَ فَكَتَبَ إِلَيَّ عُمَرُ إِنْ عَفَا فَأَجِزْ عَفْوَهُ فِي نَفْسِهِ وَإِنْ افْتُرِيَ عَلَى أَبَوَيْهِ وَقَدْ هَلَكَا أَوْ أَحَدُهُمَا فَخُذْ لَهُ بِكِتَابِ اللهِ إِلَّا أَنْ يُرِيدَ سِتْرًا قَالَ يَحْيَى سَمِعْت مَا لِكًا يَقُولُ وَذَلِكَ أَنْ يَكُونَ الرَّجُلُ الْمُفْتَرَى عَلَيْهِ يَخَافُ إِنْ كُشِفَ ذَلِكَ مِنْهُ أَنْ تَقُومَ عَلَيْهِ بَيِّنَةٌ فَإِذَا كَانَ عَلَى مَا وَصَفْتُ فَعَفَا جَازَ عَفْوُهُ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>এক ব্যক্তি, যার নাম মিসবাহ, স্বীয় ছেলেকে কোন কাজে ডাকলেন। সে আসতে বিলম্ব করল। সে যখন এল, তখন মিসবাহ তাকে বলল, হে ব্যভিচারী! যুরাইক বলেন, এ ছেলেটি আমার কাছে ফরিয়াদ করল। আমি যখন তার পিতাকে শাস্তি দিতে চাইলাম, সে বলতে লাগল, যদি তুমি আমার পিতাকে বেত্রাঘাত কর, তা হলে আমি ব্যভিচারের স্বীকারোক্তি করব। এটা শুনে আমি মুশকিলে পড়ে গেলাম আর এই ঝগড়ার ফয়সালা করা কষ্টকর হয়ে পড়ল। বিষয়টি আমি উমার ইব্নু আবদুল আযীয (র)-কে লিখে জানালাম। ঐ সময় তিনি মদীনার শাসনকর্তা ছিলেন। উমার ইব্নু আবদুল আযীয (র) উত্তরে লিখলেন, ছেলেকে ক্ষমা কর। যুরাইক বলেন, আমি উমারকে ইহাও লিখলাম, যদি কোন ব্যক্তি কাউকে অথবা তার পিতাকে অথবা তার মাতাকে ব্যভিচারের অপবাদ দেয় আর তার মাতাপিতা মৃত্যুবরণ করে অথবা তাদের একজন মৃত্যুবরণ করে থাকে (তা হলে এর বিধান কি?), তখন উমার (রা) উত্তরে লিখলেন, যাকে অপবাদ দেয়া হয়েছে, যদি সে ক্ষমা করে, তবে ক্ষমা ঠিকই হবে। হ্যাঁ, যদি তার মাতাপিতা উভয়ে অথবা কোন একজন মৃত্যুবরণ করে থাকে, তবে আল্লাহ্‌র কিতাবের বিধান মতে তার শাস্তি হবে। হ্যাঁ, যদি ছেলে স্বীয় পিতার অবস্থা লুকাবার জন্য ক্ষমা করে তবে ক্ষমা বৈধ হবে। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) ইয়াহইয়া বলেন, আমি মালিক (র)-কে বলতে শুনেছি ইহা এজন্য যে, যাকে অপবাদ দেয়া হয়েছে, যদি অপবাদের কথা প্রকাশ পায় শাস্তি দেয়ার কারণে এবং আশংকা করা হয় যে, এতে ব্যভিচারের সাক্ষী প্রকাশ পেয়ে যাবে আর ছেলে তা লুকাতে চাইবে। তাকে ক্ষমা করে দেয়া বৈধ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1524</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي مَالِك عَنْ هِشَامِ بْنِ عُرْوَةَ عَنْ أَبِيهِ أَنَّهُ قَالَ فِي رَجُلٍ قَذَفَ قَوْمًا جَمَاعَةً أَنَّهُ لَيْسَ عَلَيْهِ إِلَّا حَدٌّ وَاحِدٌ قَالَ مَالِك وَإِنْ تَفَرَّقُوا فَلَيْسَ عَلَيْهِ إِلَّا حَدٌّ وَاحِدٌ حَدَّثَنِي مَالِك عَنْ أَبِي الرِّجَالِ مُحَمَّدِ بْنِ عَبْدِ الرَّحْمَنِ بْنِ حَارِثَةَ بْنِ النُّعْمَانِ الْأَنْصَارِيِّ ثُمَّ مِنْ بَنِي النَّجَّارِ عَنْ أُمِّهِ عَمْرَةَ بِنْتِ عَبْدِ الرَّحْمَنِ أَنَّ رَجُلَيْنِ اسْتَبَّا فِي زَمَانِ عُمَرَ بْنِ الْخَطَّابِ فَقَالَ أَحَدُهُمَا لِلْآخَرِ وَاللهِ مَا أَبِي بِزَانٍ وَلَا أُمِّي بِزَانِيَةٍ فَاسْتَشَارَ فِي ذَلِكَ عُمَرُ بْنُ الْخَطَّابِ فَقَالَ قَائِلٌ مَدَحَ أَبَاهُ وَأُمَّهُ وَقَالَ آخَرُونَ قَدْ كَانَ لِأَبِيهِ وَأُمِّهِ مَدْحٌ غَيْرُ هَذَا نَرَى أَنْ تَجْلِدَهُ الْحَدَّ فَجَلَدَهُ عُمَرُ الْحَدَّ ثَمَانِينَ قَالَ مَالِك لَا حَدَّ عِنْدَنَا إِلَّا فِي نَفْيٍ أَوْ قَذْفٍ أَوْ تَعْرِيضٍ يُرَى أَنَّ قَائِلَهُ إِنَّمَا أَرَادَ بِذَلِكَ نَفْيًا أَوْ قَذْفًا فَعَلَى مَنْ قَالَ ذَلِكَ الْحَدُّ تَامًّا قَالَ مَالِك الْأَمْرُ عِنْدَنَا أَنَّهُ إِذَا نَفَى رَجُلٌ رَجُلًا مِنْ أَبِيهِ فَإِنَّ عَلَيْهِ الْحَدَّ وَإِنْ كَانَتْ أُمُّ الَّذِي نُفِيَ مَمْلُوكَةً فَإِنَّ عَلَيْهِ الْحَدَّ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>যে ব্যক্তি এক কথায়ই অনেক লোকের উপর ব্যভিচারের অপবাদ দেয়, যেমন বলল, তোমরা সকলে ব্যভিচারী অথবা হে ব্যভিচারীর দল, তা হলে তার উপর অপবাদের এক শাস্তিই হবে। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন) মালিক (র) বলেন, যদি তারা পৃথকও হয়ে যায়, তবুও একই শাস্তি হবে। আমারা বিন্তে আবদুর রহমান (র) বলেন, উমার (রা)-এর সময় দুই ব্যক্তির মধ্যে গালমন্দ হল। একজন অপরজনকে বলল,, আল্লাহ্‌র কসম, আমার পিতা বদকার ছিল না, আমার মাও বদকার ছিল না। উমার (রা) এ ব্যাপারে পরামর্শ করলেন। এক ব্যক্তি বলল, এতে সে মন্দ কি বলল। সে তো স্বীয় মাতাপিতার ভালই বর্ণনা করল। অন্যরা বলল, তার পিতার কি এই গুণ ছাড়া অন্যকোন গুণ অবশিষ্ট ছিল না? আমাদের মতে তাকে অপবাদের শাস্তি দিতে হবে। অবশেষে উমার (রা) তাকে আশি বেত্রাঘাত লাগালেন। মালিক (র) বলেন, আমাদের মতে অপবাদ, অস্বীকার ও ইশারায় গালি ছাড়া অন্য কোন কথায় শাস্তি অনিবার্য হয় না। মালিক (র) বলেন, আমার মতে যদি কেউ কাউকে তার পিতার বংশের বলে অস্বীকার করে, তা হলে শাস্তি ওয়াজিব হবে, তার মা দাসী হলেও।</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي مَالِك عَنْ رَبِيعَةَ بْنِ أَبِي عَبْدِ الرَّحْمَنِ أَنَّ عُمَرَ بْنَ الْخَطَّابِ قَالَ لِرَجُلٍ خَرَجَ بِجَارِيَةٍ لِامْرَأَتِهِ مَعَهُ فِي سَفَرٍ فَأَصَابَهَا فَغَارَتْ امْرَأَتُهُ فَذَكَرَتْ ذَلِكَ لِعُمَرَ بْنِ الْخَطَّابِ فَسَأَلَهُ عَنْ ذَلِكَ فَقَالَ وَهَبَتْهَا لِي فَقَالَ عُمَرُ لَتَأْتِينِي بِالْبَيِّنَةِ أَوْ لَأَرْمِيَنَّكَ بِالْحِجَارَةِ قَالَ فَاعْتَرَفَتْ امْرَأَتُهُ أَنَّهَا وَهَبَتْهَا لَهُ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>এক ব্যক্তি তার স্ত্রীর দাসীকে সাথে নিয়ে সফরে যাত্রা করল। তথায় সে তার সাথে সহবাস করে বসল। স্ত্রী হিংসার বশবর্তী হয়ে উমার (রা)-এর কাছে বলে দিল। উমার (রা) তাকে এ ব্যাপারে প্রশ্ন করলে সে বলল, আমার স্ত্রী এই দাসীটি আমাকে দান করেছে। উমার (রা) বললেন, তুমি দানের সাক্ষী নিয়ে এসো, না হয় তোমাকে প্রস্তরাঘাত করা হবে। তখন স্ত্রীলোকটি বলল, আমি তাকে দান করেছি। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1539</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي عَنْ مَالِك عَنْ ابْنِ شِهَابٍ أَنَّ مَرْوَانَ بْنَ الْحَكَمِ أُتِيَ بِإِنْسَانٍ قَدْ اخْتَلَسَ مَتَاعًا فَأَرَادَ قَطْعَ يَدِهِ فَأَرْسَلَ إِلَى زَيْدِ بْنِ ثَابِتٍ يَسْأَلُهُ عَنْ ذَلِكَ فَقَالَ زَيْدُ بْنُ ثَابِتٍ لَيْسَ فِي الْخُلْسَةِ قَطْعٌ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>মারওয়ানের নিকট এক ব্যক্তিকে আনা হল, যে ব্যক্তি কারো মাল অপহরণ করে নিয়ে গিয়েছে। মারওয়ান তার হাত কাটতে মনস্থ করলেন। অতঃপর এর বিধান জিজ্ঞেস করবার জন্য যায়দ ইব্নু সাবিত (র)-এর নিকট এক ব্যক্তিকে পাঠালেন। তিনি বললেন, যে ব্যক্তি কারো মাল অপহরণ করে, তার হাত কাটা হবে না। [১] (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي عَنْ مَالِك عَنْ عَمِّهِ أَبِي سُهَيْلِ بْنِ مَالِكٍ عَنْ أَبِيهِ عَنْ كَعْبِ الْأَحْبَارِ أَنَّ رَجُلًا نَزَعَ نَعْلَيْهِ فَقَالَ لِمَ خَلَعْتَ نَعْلَيْكَ لَعَلَّكَ تَأَوَّلْتَ هَذِهِ الْآيَةَ { فَاخْلَعْ نَعْلَيْكَ إِنَّكَ بِالْوَادِ الْمُقَدَّسِ طُوًى } قَالَ ثُمَّ قَالَ كَعْبٌ لِلرَّجُلِ أَتَدْرِي مَا كَانَتْ نَعْلَا مُوسَى قَالَ مَالِك لَا أَدْرِي مَا أَجَابَهُ الرَّجُلُ فَقَالَ كَعْبٌ كَانَتَا مِنْ جِلْدِ حِمَارٍ مَيِّتٍ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>এক ব্যক্তি নিজের জুতা খুলল। কা‘ব তাকে বলল, তুমি তোমার জুতা কেন খুলে ফেলেছ ? হয়ত তুমি, فَاخْلَعْ نَعْلَيْكَ إِنَّكَ بِالْوَادِ الْمُقَدَّسِ طُوًى “আমি তোমার প্রভু। তুমি তোমার জুতা খুলে ফেল। কেননা তুমি ‘তুয়া’ নামক পবিত্র ভূমিতে আছ।” এই আয়াত দেখে জুতা খুলেছ। অতঃপর কা’ব বললেন, তোমার জানা আছে কি মূসা (আ)-এর জুতা কিসের ছিল ? মালিক (র) বললেন, আমার জানা নেই, ঐ ব্যক্তি কি উত্তর দিয়েছিল। অতঃপর কা‘ব বললেন, উহা মৃত গাধার চামড়া দ্বারা প্রস্তুত করা হয়েছিল। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন, হাদীসটিতে ইসরাঈলী বর্ণনা রয়েছে)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1646</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي عَنْ مَالِك عَنْ إِسْحَقَ بْنِ عَبْدِ اللهِ بْنِ أَبِي طَلْحَةَ أَنَّهُ قَالَ قَالَ أَنَسُ بْنُ مَالِكٍ رَأَيْتُ عُمَرَ بْنَ الْخَطَّابِ وَهُوَ يَوْمَئِذٍ أَمِيرُ الْمَدِينَةِ وَقَدْ رَقَعَ بَيْنَ كَتِفَيْهِ بِرِقَاعٍ ثَلَاثٍ لَبَّدَ بَعْضَهَا فَوْقَ بَعْضٍ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>আমি উমার (রা)-কে দেখেছি তখন তিনি মদীনাতে আমীরুল মু‘মিনীন ছিলেন। আর তখন তাঁর জামায় স্কন্ধের মধ্যস্থলে পর পর তিনটি তালি লাগানো ছিল। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1659</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>حَدَّثَنِي عَنْ مَالِك أَنَّهُ بَلَغَهُ أَنَّ عُمَرَ بْنَ الْخَطَّابِ وَعَلِيَّ بْنَ أَبِي طَالِبٍ وَعُثْمَانَ بْنَ عَفَّانَ كَانُوا يَشْرَبُونَ قِيَامًاِِِِ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>উমার ইব্নু খাত্তাব (রা), আলী ইব্নু আবী তালিব (রা) ও উসমান ইব্নু আফফান (রা) দাঁড়িয়ে পানি পান করতেন। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1660</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>و حَدَّثَنِي عَنْ مَالِك عَنْ ابْنِ شِهَابٍ أَنَّ عَائِشَةَ أُمَّ الْمُؤْمِنِينَ وَسَعْدَ بْنَ أَبِي وَقَّاصٍ كَانَا لَا يَرَيَانِ بِشُرْبِ الْإِنْسَانِ وَهُوَ قَائِمٌ بَأْسًاِِِِ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>উম্মুল মু’মিনীন আয়িশা (রা) ও সা‘দ ইব্নু আবী ওয়াক্কাস (রা) দাঁড়িয়ে পানি পান করাকে খারাপ মনে করতেন না। (হাদীসটি ইমাম মালিক এককভাবে বর্ণনা করেছেন)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
